--- a/Datas/MoneyCreatData.xlsx
+++ b/Datas/MoneyCreatData.xlsx
@@ -12,11 +12,11 @@
     <workbookView xWindow="240" yWindow="135" windowWidth="9675" windowHeight="7380"/>
   </bookViews>
   <sheets>
-    <sheet name="item" sheetId="1" r:id="rId1"/>
+    <sheet name="MoneyCreatData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">item!$A$3:$C$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MoneyCreatData!$A$3:$C$3</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>

--- a/Datas/MoneyCreatData.xlsx
+++ b/Datas/MoneyCreatData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -66,8 +66,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Golds</t>
+    <t>Gold0</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold1</t>
+  </si>
+  <si>
+    <t>Gold2</t>
+  </si>
+  <si>
+    <t>Gold3</t>
+  </si>
+  <si>
+    <t>Gold4</t>
+  </si>
+  <si>
+    <t>Gold5</t>
   </si>
 </sst>
 </file>
@@ -526,7 +541,7 @@
         <v>8002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -550,7 +565,7 @@
         <v>8003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -574,7 +589,7 @@
         <v>8004</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -598,7 +613,7 @@
         <v>8005</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -622,7 +637,7 @@
         <v>8006</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
